--- a/PROPUESTA_PRODUCCION_SUBLIMADO_ACTUALIZADA.xlsx
+++ b/PROPUESTA_PRODUCCION_SUBLIMADO_ACTUALIZADA.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +29,38 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <color rgb="000000FF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -50,8 +75,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,11 +465,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Género</t>
         </is>
@@ -433,17 +481,17 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>SUGERIDO</t>
+          <t>SUGERIDO (MÍN)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>MÍNIMO</t>
+          <t>MÁXIMO</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>MÁXIMO</t>
+          <t>Rango</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -459,16 +507,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>408</v>
+        <v>349</v>
       </c>
       <c r="C2" t="n">
-        <v>583</v>
+        <v>524</v>
       </c>
       <c r="D2" t="n">
-        <v>505</v>
+        <v>637</v>
       </c>
       <c r="E2" t="n">
-        <v>661</v>
+        <v>113</v>
       </c>
       <c r="F2" t="n">
         <v>175</v>
@@ -481,19 +529,41 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="C3" t="n">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="D3" t="n">
-        <v>220</v>
+        <v>307</v>
       </c>
       <c r="E3" t="n">
-        <v>314</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>99</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>485</v>
+      </c>
+      <c r="C4" t="n">
+        <v>772</v>
+      </c>
+      <c r="D4" t="n">
+        <v>944</v>
+      </c>
+      <c r="E4" t="n">
+        <v>172</v>
+      </c>
+      <c r="F4" t="n">
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -507,532 +577,354 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rango de producción MÍNIMO / MÁXIMO — Short Playa Sublimado (CAB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Factor de temporada alta</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SUGERIDO —</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Playuela</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>12</v>
-      </c>
-      <c r="C3" t="n">
-        <v>40</v>
-      </c>
-      <c r="D3" t="n">
-        <v>46</v>
-      </c>
-      <c r="E3" t="n">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Playuela — MÍNIMO</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="F3" t="n">
-        <v>15</v>
-      </c>
-      <c r="G3" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sal (Cayo Sal)</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>13</v>
-      </c>
-      <c r="C4" t="n">
-        <v>33</v>
-      </c>
-      <c r="D4" t="n">
-        <v>49</v>
-      </c>
-      <c r="E4" t="n">
-        <v>28</v>
-      </c>
-      <c r="F4" t="n">
-        <v>21</v>
-      </c>
-      <c r="G4" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tucupido</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>24</v>
-      </c>
-      <c r="D5" t="n">
-        <v>24</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Nuevo Diseño</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>32</v>
-      </c>
-      <c r="C6" t="n">
-        <v>71</v>
-      </c>
-      <c r="D6" t="n">
-        <v>71</v>
-      </c>
-      <c r="E6" t="n">
-        <v>54</v>
-      </c>
-      <c r="F6" t="n">
-        <v>29</v>
-      </c>
-      <c r="G6" t="n">
-        <v>257</v>
+      <c r="F6" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" s="6">
+        <f>SUM(B6:F6)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>58</v>
-      </c>
-      <c r="C7" t="n">
-        <v>168</v>
-      </c>
-      <c r="D7" t="n">
-        <v>190</v>
-      </c>
-      <c r="E7" t="n">
-        <v>99</v>
-      </c>
-      <c r="F7" t="n">
-        <v>68</v>
-      </c>
-      <c r="G7" t="n">
-        <v>583</v>
+          <t xml:space="preserve">Playuela — MÁXIMO </t>
+        </is>
+      </c>
+      <c r="B7" s="7">
+        <f>IF(B6="","",ROUND(B6*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="C7" s="7">
+        <f>IF(C6="","",ROUND(C6*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="D7" s="7">
+        <f>IF(D6="","",ROUND(D6*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="E7" s="7">
+        <f>IF(E6="","",ROUND(E6*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="F7" s="7">
+        <f>IF(F6="","",ROUND(F6*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="G7" s="7">
+        <f>SUM(B7:F7)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2XL</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Sal — MÍNIMO</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="G8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MÍNIMO —</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+          <t xml:space="preserve">Sal — MÁXIMO </t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>IF(B8="","",ROUND(B8*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="C9" s="7">
+        <f>IF(C8="","",ROUND(C8*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="D9" s="7">
+        <f>IF(D8="","",ROUND(D8*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="E9" s="7">
+        <f>IF(E8="","",ROUND(E8*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="F9" s="7">
+        <f>IF(F8="","",ROUND(F8*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="G9" s="7">
+        <f>SUM(B9:F9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Playuela</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>10</v>
-      </c>
-      <c r="C10" t="n">
-        <v>35</v>
-      </c>
-      <c r="D10" t="n">
-        <v>40</v>
-      </c>
-      <c r="E10" t="n">
-        <v>11</v>
-      </c>
-      <c r="F10" t="n">
-        <v>13</v>
-      </c>
-      <c r="G10" t="n">
-        <v>109</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Tucupido — MÍNIMO</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="6">
+        <f>SUM(B10:F10)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sal (Cayo Sal)</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>11</v>
-      </c>
-      <c r="C11" t="n">
-        <v>29</v>
-      </c>
-      <c r="D11" t="n">
-        <v>43</v>
-      </c>
-      <c r="E11" t="n">
-        <v>24</v>
-      </c>
-      <c r="F11" t="n">
-        <v>18</v>
-      </c>
-      <c r="G11" t="n">
-        <v>125</v>
+          <t xml:space="preserve">Tucupido — MÁXIMO </t>
+        </is>
+      </c>
+      <c r="B11" s="7">
+        <f>IF(B10="","",ROUND(B10*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="C11" s="7">
+        <f>IF(C10="","",ROUND(C10*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="D11" s="7">
+        <f>IF(D10="","",ROUND(D10*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="E11" s="7">
+        <f>IF(E10="","",ROUND(E10*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="F11" s="7">
+        <f>IF(F10="","",ROUND(F10*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="G11" s="7">
+        <f>SUM(B11:F11)</f>
+        <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Tucupido</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>21</v>
-      </c>
-      <c r="D12" t="n">
-        <v>21</v>
-      </c>
-      <c r="E12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" t="n">
-        <v>47</v>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Nuevo color — MÍNIMO</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="G12" s="6">
+        <f>SUM(B12:F12)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nuevo Diseño</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>28</v>
-      </c>
-      <c r="C13" t="n">
-        <v>62</v>
-      </c>
-      <c r="D13" t="n">
-        <v>62</v>
-      </c>
-      <c r="E13" t="n">
-        <v>47</v>
-      </c>
-      <c r="F13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G13" t="n">
-        <v>224</v>
+          <t xml:space="preserve">Nuevo color — MÁXIMO </t>
+        </is>
+      </c>
+      <c r="B13" s="7">
+        <f>IF(B12="","",ROUND(B12*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="C13" s="7">
+        <f>IF(C12="","",ROUND(C12*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="D13" s="7">
+        <f>IF(D12="","",ROUND(D12*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="E13" s="7">
+        <f>IF(E12="","",ROUND(E12*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="F13" s="7">
+        <f>IF(F12="","",ROUND(F12*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="G13" s="7">
+        <f>SUM(B13:F13)</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>49</v>
-      </c>
-      <c r="C14" t="n">
-        <v>147</v>
-      </c>
-      <c r="D14" t="n">
-        <v>166</v>
-      </c>
-      <c r="E14" t="n">
-        <v>85</v>
-      </c>
-      <c r="F14" t="n">
-        <v>58</v>
-      </c>
-      <c r="G14" t="n">
-        <v>505</v>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL — MÍNIMO</t>
+        </is>
+      </c>
+      <c r="B14" s="9">
+        <f>B6+B8+B10+B12</f>
+        <v/>
+      </c>
+      <c r="C14" s="9">
+        <f>C6+C8+C10+C12</f>
+        <v/>
+      </c>
+      <c r="D14" s="9">
+        <f>D6+D8+D10+D12</f>
+        <v/>
+      </c>
+      <c r="E14" s="9">
+        <f>E6+E8+E10+E12</f>
+        <v/>
+      </c>
+      <c r="F14" s="9">
+        <f>F6+F8+F10+F12</f>
+        <v/>
+      </c>
+      <c r="G14" s="9">
+        <f>G6+G8+G10+G12</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2XL</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MÁXIMO —</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Playuela</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>14</v>
-      </c>
-      <c r="C17" t="n">
-        <v>45</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
-      </c>
-      <c r="E17" t="n">
-        <v>15</v>
-      </c>
-      <c r="F17" t="n">
-        <v>17</v>
-      </c>
-      <c r="G17" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Sal (Cayo Sal)</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>15</v>
-      </c>
-      <c r="C18" t="n">
-        <v>37</v>
-      </c>
-      <c r="D18" t="n">
-        <v>55</v>
-      </c>
-      <c r="E18" t="n">
-        <v>32</v>
-      </c>
-      <c r="F18" t="n">
-        <v>24</v>
-      </c>
-      <c r="G18" t="n">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Tucupido</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>27</v>
-      </c>
-      <c r="D19" t="n">
-        <v>27</v>
-      </c>
-      <c r="E19" t="n">
-        <v>5</v>
-      </c>
-      <c r="F19" t="n">
-        <v>4</v>
-      </c>
-      <c r="G19" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Nuevo Diseño</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>36</v>
-      </c>
-      <c r="C20" t="n">
-        <v>80</v>
-      </c>
-      <c r="D20" t="n">
-        <v>80</v>
-      </c>
-      <c r="E20" t="n">
-        <v>61</v>
-      </c>
-      <c r="F20" t="n">
-        <v>33</v>
-      </c>
-      <c r="G20" t="n">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>67</v>
-      </c>
-      <c r="C21" t="n">
-        <v>189</v>
-      </c>
-      <c r="D21" t="n">
-        <v>214</v>
-      </c>
-      <c r="E21" t="n">
-        <v>113</v>
-      </c>
-      <c r="F21" t="n">
-        <v>78</v>
-      </c>
-      <c r="G21" t="n">
-        <v>661</v>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL — MÁXIMO</t>
+        </is>
+      </c>
+      <c r="B15" s="11">
+        <f>B7+B9+B11+B13</f>
+        <v/>
+      </c>
+      <c r="C15" s="11">
+        <f>C7+C9+C11+C13</f>
+        <v/>
+      </c>
+      <c r="D15" s="11">
+        <f>D7+D9+D11+D13</f>
+        <v/>
+      </c>
+      <c r="E15" s="11">
+        <f>E7+E9+E11+E13</f>
+        <v/>
+      </c>
+      <c r="F15" s="11">
+        <f>F7+F9+F11+F13</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
+        <f>G7+G9+G11+G13</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1046,658 +938,429 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rango de producción MÍNIMO / MÁXIMO — Short Playa Sublimado (KIDS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Factor de temporada alta</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SUGERIDO —</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Playuela</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Playuela — MÍNIMO</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G6" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="I3" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sal (Cayo Sal)</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I4" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tucupido</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>16</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Nuevo Diseño</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>16</v>
-      </c>
-      <c r="D6" t="n">
-        <v>29</v>
-      </c>
-      <c r="E6" t="n">
-        <v>29</v>
-      </c>
-      <c r="F6" t="n">
-        <v>21</v>
-      </c>
-      <c r="G6" t="n">
-        <v>32</v>
-      </c>
-      <c r="H6" t="n">
-        <v>32</v>
-      </c>
-      <c r="I6" t="n">
-        <v>175</v>
+      <c r="I6" s="6">
+        <f>SUM(B6:H6)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>19</v>
-      </c>
-      <c r="C7" t="n">
-        <v>36</v>
-      </c>
-      <c r="D7" t="n">
-        <v>36</v>
-      </c>
-      <c r="E7" t="n">
-        <v>36</v>
-      </c>
-      <c r="F7" t="n">
-        <v>38</v>
-      </c>
-      <c r="G7" t="n">
-        <v>49</v>
-      </c>
-      <c r="H7" t="n">
-        <v>53</v>
-      </c>
-      <c r="I7" t="n">
-        <v>267</v>
+          <t xml:space="preserve">Playuela — MÁXIMO </t>
+        </is>
+      </c>
+      <c r="B7" s="7">
+        <f>IF(B6="","",ROUND(B6*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="C7" s="7">
+        <f>IF(C6="","",ROUND(C6*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="D7" s="7">
+        <f>IF(D6="","",ROUND(D6*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="E7" s="7">
+        <f>IF(E6="","",ROUND(E6*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="F7" s="7">
+        <f>IF(F6="","",ROUND(F6*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="G7" s="7">
+        <f>IF(G6="","",ROUND(G6*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="H7" s="7">
+        <f>IF(H6="","",ROUND(H6*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="I7" s="7">
+        <f>SUM(B7:H7)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Sal — MÍNIMO</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I8" s="6">
+        <f>SUM(B8:H8)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MÍNIMO —</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t xml:space="preserve">Sal — MÁXIMO </t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>IF(B8="","",ROUND(B8*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="C9" s="7">
+        <f>IF(C8="","",ROUND(C8*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="D9" s="7">
+        <f>IF(D8="","",ROUND(D8*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="E9" s="7">
+        <f>IF(E8="","",ROUND(E8*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="F9" s="7">
+        <f>IF(F8="","",ROUND(F8*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="G9" s="7">
+        <f>IF(G8="","",ROUND(G8*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="H9" s="7">
+        <f>IF(H8="","",ROUND(H8*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="I9" s="7">
+        <f>SUM(B9:H9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Playuela</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>9</v>
-      </c>
-      <c r="G10" t="n">
-        <v>7</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>23</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Tucupido — MÍNIMO</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" s="6">
+        <f>SUM(B10:H10)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sal (Cayo Sal)</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>9</v>
-      </c>
-      <c r="I11" t="n">
+          <t xml:space="preserve">Tucupido — MÁXIMO </t>
+        </is>
+      </c>
+      <c r="B11" s="7">
+        <f>IF(B10="","",ROUND(B10*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="C11" s="7">
+        <f>IF(C10="","",ROUND(C10*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="D11" s="7">
+        <f>IF(D10="","",ROUND(D10*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="E11" s="7">
+        <f>IF(E10="","",ROUND(E10*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="F11" s="7">
+        <f>IF(F10="","",ROUND(F10*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="G11" s="7">
+        <f>IF(G10="","",ROUND(G10*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="H11" s="7">
+        <f>IF(H10="","",ROUND(H10*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="I11" s="7">
+        <f>SUM(B11:H11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Nuevo color — MÍNIMO</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="5" t="n">
         <v>21</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Tucupido</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>14</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" t="n">
-        <v>24</v>
+      <c r="E12" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="I12" s="6">
+        <f>SUM(B12:H12)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nuevo Diseño</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="n">
-        <v>14</v>
-      </c>
-      <c r="D13" t="n">
-        <v>25</v>
-      </c>
-      <c r="E13" t="n">
-        <v>25</v>
-      </c>
-      <c r="F13" t="n">
-        <v>18</v>
-      </c>
-      <c r="G13" t="n">
-        <v>28</v>
-      </c>
-      <c r="H13" t="n">
-        <v>28</v>
-      </c>
-      <c r="I13" t="n">
-        <v>152</v>
+          <t xml:space="preserve">Nuevo color — MÁXIMO </t>
+        </is>
+      </c>
+      <c r="B13" s="7">
+        <f>IF(B12="","",ROUND(B12*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="C13" s="7">
+        <f>IF(C12="","",ROUND(C12*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="D13" s="7">
+        <f>IF(D12="","",ROUND(D12*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="E13" s="7">
+        <f>IF(E12="","",ROUND(E12*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="F13" s="7">
+        <f>IF(F12="","",ROUND(F12*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="G13" s="7">
+        <f>IF(G12="","",ROUND(G12*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="H13" s="7">
+        <f>IF(H12="","",ROUND(H12*$B$3,0))</f>
+        <v/>
+      </c>
+      <c r="I13" s="7">
+        <f>SUM(B13:H13)</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="n">
-        <v>30</v>
-      </c>
-      <c r="D14" t="n">
-        <v>29</v>
-      </c>
-      <c r="E14" t="n">
-        <v>29</v>
-      </c>
-      <c r="F14" t="n">
-        <v>31</v>
-      </c>
-      <c r="G14" t="n">
-        <v>42</v>
-      </c>
-      <c r="H14" t="n">
-        <v>45</v>
-      </c>
-      <c r="I14" t="n">
-        <v>220</v>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL — MÍNIMO</t>
+        </is>
+      </c>
+      <c r="B14" s="9">
+        <f>B6+B8+B10+B12</f>
+        <v/>
+      </c>
+      <c r="C14" s="9">
+        <f>C6+C8+C10+C12</f>
+        <v/>
+      </c>
+      <c r="D14" s="9">
+        <f>D6+D8+D10+D12</f>
+        <v/>
+      </c>
+      <c r="E14" s="9">
+        <f>E6+E8+E10+E12</f>
+        <v/>
+      </c>
+      <c r="F14" s="9">
+        <f>F6+F8+F10+F12</f>
+        <v/>
+      </c>
+      <c r="G14" s="9">
+        <f>G6+G8+G10+G12</f>
+        <v/>
+      </c>
+      <c r="H14" s="9">
+        <f>H6+H8+H10+H12</f>
+        <v/>
+      </c>
+      <c r="I14" s="9">
+        <f>I6+I8+I10+I12</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MÁXIMO —</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Playuela</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" t="n">
-        <v>13</v>
-      </c>
-      <c r="G17" t="n">
-        <v>9</v>
-      </c>
-      <c r="H17" t="n">
-        <v>6</v>
-      </c>
-      <c r="I17" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Sal (Cayo Sal)</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5</v>
-      </c>
-      <c r="G18" t="n">
-        <v>8</v>
-      </c>
-      <c r="H18" t="n">
-        <v>13</v>
-      </c>
-      <c r="I18" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Tucupido</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>18</v>
-      </c>
-      <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>4</v>
-      </c>
-      <c r="F19" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H19" t="n">
-        <v>6</v>
-      </c>
-      <c r="I19" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Nuevo Diseño</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>18</v>
-      </c>
-      <c r="C20" t="n">
-        <v>18</v>
-      </c>
-      <c r="D20" t="n">
-        <v>33</v>
-      </c>
-      <c r="E20" t="n">
-        <v>33</v>
-      </c>
-      <c r="F20" t="n">
-        <v>24</v>
-      </c>
-      <c r="G20" t="n">
-        <v>36</v>
-      </c>
-      <c r="H20" t="n">
-        <v>36</v>
-      </c>
-      <c r="I20" t="n">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>24</v>
-      </c>
-      <c r="C21" t="n">
-        <v>42</v>
-      </c>
-      <c r="D21" t="n">
-        <v>43</v>
-      </c>
-      <c r="E21" t="n">
-        <v>43</v>
-      </c>
-      <c r="F21" t="n">
-        <v>45</v>
-      </c>
-      <c r="G21" t="n">
-        <v>56</v>
-      </c>
-      <c r="H21" t="n">
-        <v>61</v>
-      </c>
-      <c r="I21" t="n">
-        <v>314</v>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL — MÁXIMO</t>
+        </is>
+      </c>
+      <c r="B15" s="11">
+        <f>B7+B9+B11+B13</f>
+        <v/>
+      </c>
+      <c r="C15" s="11">
+        <f>C7+C9+C11+C13</f>
+        <v/>
+      </c>
+      <c r="D15" s="11">
+        <f>D7+D9+D11+D13</f>
+        <v/>
+      </c>
+      <c r="E15" s="11">
+        <f>E7+E9+E11+E13</f>
+        <v/>
+      </c>
+      <c r="F15" s="11">
+        <f>F7+F9+F11+F13</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
+        <f>G7+G9+G11+G13</f>
+        <v/>
+      </c>
+      <c r="H15" s="11">
+        <f>H7+H9+H11+H13</f>
+        <v/>
+      </c>
+      <c r="I15" s="11">
+        <f>I7+I9+I11+I13</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1711,7 +1374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1732,7 +1395,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Sugerido</t>
+          <t>Sugerido (MÍN)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -1756,10 +1419,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -1774,13 +1437,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -1795,13 +1458,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -1840,16 +1503,16 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sal (Cayo Sal)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1861,16 +1524,16 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sal (Cayo Sal)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1879,19 +1542,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sal (Cayo Sal)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1900,19 +1563,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sal (Cayo Sal)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1933,7 +1596,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sal (Cayo Sal)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1959,17 +1622,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1980,17 +1643,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -2001,164 +1664,122 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>2XL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tucupido</t>
+          <t>Nuevo color</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tucupido</t>
+          <t>Nuevo color</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nuevo Diseño</t>
+          <t>Nuevo color</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="D17" t="n">
+        <v>77</v>
+      </c>
+      <c r="E17" t="n">
         <v>32</v>
-      </c>
-      <c r="E17" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nuevo Diseño</t>
+          <t>Nuevo color</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nuevo Diseño</t>
+          <t>Nuevo color</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>2XL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="D19" t="n">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Nuevo Diseño</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>41</v>
-      </c>
-      <c r="D20" t="n">
-        <v>54</v>
-      </c>
-      <c r="E20" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Nuevo Diseño</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2XL</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>22</v>
-      </c>
-      <c r="D21" t="n">
-        <v>29</v>
-      </c>
-      <c r="E21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2172,7 +1793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2193,7 +1814,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Sugerido</t>
+          <t>Sugerido (MÍN)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -2217,10 +1838,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -2238,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2259,10 +1880,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -2280,10 +1901,10 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2352,7 +1973,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sal (Cayo Sal)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2364,16 +1985,16 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sal (Cayo Sal)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2385,16 +2006,16 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sal (Cayo Sal)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2406,16 +2027,16 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sal (Cayo Sal)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2427,16 +2048,16 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sal (Cayo Sal)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2457,7 +2078,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sal (Cayo Sal)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2478,7 +2099,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sal (Cayo Sal)</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2504,17 +2125,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -2525,269 +2146,164 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tucupido</t>
+          <t>Nuevo color</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
+        <v>13</v>
+      </c>
+      <c r="E18" t="n">
         <v>3</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tucupido</t>
+          <t>Nuevo color</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tucupido</t>
+          <t>Nuevo color</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tucupido</t>
+          <t>Nuevo color</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tucupido</t>
+          <t>Nuevo color</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D22" t="n">
+        <v>21</v>
+      </c>
+      <c r="E22" t="n">
         <v>5</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nuevo Diseño</t>
+          <t>Nuevo color</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nuevo Diseño</t>
+          <t>Nuevo color</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D24" t="n">
+        <v>32</v>
+      </c>
+      <c r="E24" t="n">
         <v>12</v>
-      </c>
-      <c r="D24" t="n">
-        <v>16</v>
-      </c>
-      <c r="E24" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Nuevo Diseño</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>22</v>
-      </c>
-      <c r="D25" t="n">
-        <v>29</v>
-      </c>
-      <c r="E25" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Nuevo Diseño</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>22</v>
-      </c>
-      <c r="D26" t="n">
-        <v>29</v>
-      </c>
-      <c r="E26" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Nuevo Diseño</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>16</v>
-      </c>
-      <c r="D27" t="n">
-        <v>21</v>
-      </c>
-      <c r="E27" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Nuevo Diseño</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>24</v>
-      </c>
-      <c r="D28" t="n">
-        <v>32</v>
-      </c>
-      <c r="E28" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Nuevo Diseño</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>24</v>
-      </c>
-      <c r="D29" t="n">
-        <v>32</v>
-      </c>
-      <c r="E29" t="n">
-        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/PROPUESTA_PRODUCCION_SUBLIMADO_ACTUALIZADA.xlsx
+++ b/PROPUESTA_PRODUCCION_SUBLIMADO_ACTUALIZADA.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,6 +496,11 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>% Rango</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Δ vs equipo</t>
         </is>
       </c>
@@ -510,16 +515,19 @@
         <v>349</v>
       </c>
       <c r="C2" t="n">
-        <v>524</v>
+        <v>474</v>
       </c>
       <c r="D2" t="n">
-        <v>637</v>
+        <v>568</v>
       </c>
       <c r="E2" t="n">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="F2" t="n">
-        <v>175</v>
+        <v>19.8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>125</v>
       </c>
     </row>
     <row r="3">
@@ -532,16 +540,19 @@
         <v>136</v>
       </c>
       <c r="C3" t="n">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="D3" t="n">
-        <v>307</v>
+        <v>274</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>112</v>
+        <v>21.8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="4">
@@ -554,16 +565,19 @@
         <v>485</v>
       </c>
       <c r="C4" t="n">
-        <v>772</v>
+        <v>699</v>
       </c>
       <c r="D4" t="n">
-        <v>944</v>
+        <v>842</v>
       </c>
       <c r="E4" t="n">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="F4" t="n">
-        <v>287</v>
+        <v>20.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -650,19 +664,19 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C6" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="D6" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>37</v>
-      </c>
       <c r="E6" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>13</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>14</v>
       </c>
       <c r="G6" s="6">
         <f>SUM(B6:F6)</f>
@@ -707,19 +721,19 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G8" s="6">
         <f>SUM(B8:F8)</f>
@@ -763,14 +777,20 @@
           <t>Tucupido — MÍNIMO</t>
         </is>
       </c>
+      <c r="B10" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="C10" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>20</v>
+        <v>14</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>7</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G10" s="6">
         <f>SUM(B10:F10)</f>
@@ -815,19 +835,19 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G12" s="6">
         <f>SUM(B12:F12)</f>
@@ -1035,13 +1055,13 @@
         <v>4</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" s="6">
         <f>SUM(B6:H6)</f>
@@ -1109,10 +1129,10 @@
         <v>4</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I8" s="6">
         <f>SUM(B8:H8)</f>
@@ -1164,11 +1184,26 @@
           <t>Tucupido — MÍNIMO</t>
         </is>
       </c>
+      <c r="B10" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="C10" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I10" s="6">
         <f>SUM(B10:H10)</f>
@@ -1221,25 +1256,25 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I12" s="6">
         <f>SUM(B12:H12)</f>
@@ -1374,7 +1409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1419,10 +1454,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1440,10 +1475,10 @@
         <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -1461,10 +1496,10 @@
         <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -1482,10 +1517,10 @@
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -1503,10 +1538,10 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1524,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1545,10 +1580,10 @@
         <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -1566,10 +1601,10 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -1587,10 +1622,10 @@
         <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1608,10 +1643,10 @@
         <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="12">
@@ -1622,17 +1657,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1643,17 +1678,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="14">
@@ -1664,59 +1699,59 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nuevo color</t>
+          <t>Tucupido</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nuevo color</t>
+          <t>Tucupido</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>2XL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -1727,17 +1762,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>32</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="18">
@@ -1748,17 +1783,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E18" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -1769,17 +1804,59 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>45</v>
+      </c>
+      <c r="D19" t="n">
+        <v>73</v>
+      </c>
+      <c r="E19" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Nuevo color</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>35</v>
+      </c>
+      <c r="D20" t="n">
+        <v>36</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Nuevo color</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>2XL</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D19" t="n">
-        <v>26</v>
-      </c>
-      <c r="E19" t="n">
-        <v>6</v>
+      <c r="D21" t="n">
+        <v>24</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1793,7 +1870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1922,10 +1999,10 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="7">
@@ -1943,10 +2020,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1964,10 +2041,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -2090,10 +2167,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -2111,10 +2188,10 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="16">
@@ -2125,17 +2202,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -2146,122 +2223,122 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nuevo color</t>
+          <t>Tucupido</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nuevo color</t>
+          <t>Tucupido</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nuevo color</t>
+          <t>Tucupido</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nuevo color</t>
+          <t>Tucupido</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nuevo color</t>
+          <t>Tucupido</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -2272,17 +2349,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2293,17 +2370,122 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="n">
+        <v>19</v>
+      </c>
+      <c r="E24" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Nuevo color</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>16</v>
+      </c>
+      <c r="D25" t="n">
+        <v>19</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Nuevo color</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>16</v>
+      </c>
+      <c r="D26" t="n">
+        <v>19</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Nuevo color</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>16</v>
+      </c>
+      <c r="D27" t="n">
+        <v>19</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Nuevo color</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>20</v>
+      </c>
+      <c r="D28" t="n">
+        <v>19</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Nuevo color</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C29" t="n">
         <v>20</v>
       </c>
-      <c r="D24" t="n">
-        <v>32</v>
-      </c>
-      <c r="E24" t="n">
-        <v>12</v>
+      <c r="D29" t="n">
+        <v>30</v>
+      </c>
+      <c r="E29" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/PROPUESTA_PRODUCCION_SUBLIMADO_ACTUALIZADA.xlsx
+++ b/PROPUESTA_PRODUCCION_SUBLIMADO_ACTUALIZADA.xlsx
@@ -515,19 +515,19 @@
         <v>349</v>
       </c>
       <c r="C2" t="n">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D2" t="n">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F2" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="G2" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3">
@@ -540,19 +540,19 @@
         <v>136</v>
       </c>
       <c r="C3" t="n">
-        <v>225</v>
+        <v>305</v>
       </c>
       <c r="D3" t="n">
-        <v>274</v>
+        <v>366</v>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F3" t="n">
-        <v>21.8</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>89</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4">
@@ -565,19 +565,19 @@
         <v>485</v>
       </c>
       <c r="C4" t="n">
-        <v>699</v>
+        <v>777</v>
       </c>
       <c r="D4" t="n">
-        <v>842</v>
+        <v>933</v>
       </c>
       <c r="E4" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="F4" t="n">
-        <v>20.5</v>
+        <v>20.1</v>
       </c>
       <c r="G4" t="n">
-        <v>214</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -664,13 +664,13 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>19</v>
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G8" s="6">
         <f>SUM(B8:F8)</f>
@@ -778,19 +778,19 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="G10" s="6">
         <f>SUM(B10:F10)</f>
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>61</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G12" s="6">
         <f>SUM(B12:F12)</f>
@@ -1043,22 +1043,22 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>4</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>6</v>
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I8" s="6">
         <f>SUM(B8:H8)</f>
@@ -1194,10 +1194,10 @@
         <v>4</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>4</v>
@@ -1256,25 +1256,25 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I12" s="6">
         <f>SUM(B12:H12)</f>
@@ -1454,10 +1454,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1475,10 +1475,10 @@
         <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -1496,10 +1496,10 @@
         <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -1580,10 +1580,10 @@
         <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -1601,10 +1601,10 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -1622,10 +1622,10 @@
         <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="11">
@@ -1643,10 +1643,10 @@
         <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
@@ -1664,10 +1664,10 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1685,10 +1685,10 @@
         <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="14">
@@ -1706,10 +1706,10 @@
         <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="15">
@@ -1727,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -1748,10 +1748,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1769,10 +1769,10 @@
         <v>20</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E17" t="n">
-        <v>-8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -1811,10 +1811,10 @@
         <v>45</v>
       </c>
       <c r="D19" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1832,10 +1832,10 @@
         <v>35</v>
       </c>
       <c r="D20" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="21">
@@ -1853,10 +1853,10 @@
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1915,10 +1915,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1936,10 +1936,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1957,10 +1957,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -1999,10 +1999,10 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="7">
@@ -2020,10 +2020,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -2062,10 +2062,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -2104,10 +2104,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -2146,10 +2146,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -2167,10 +2167,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -2188,10 +2188,10 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E15" t="n">
-        <v>-2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -2272,10 +2272,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2293,10 +2293,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -2356,10 +2356,10 @@
         <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -2377,10 +2377,10 @@
         <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2398,10 +2398,10 @@
         <v>16</v>
       </c>
       <c r="D25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -2419,10 +2419,10 @@
         <v>16</v>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -2440,10 +2440,10 @@
         <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -2461,10 +2461,10 @@
         <v>20</v>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E28" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -2482,10 +2482,10 @@
         <v>20</v>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/PROPUESTA_PRODUCCION_SUBLIMADO_ACTUALIZADA.xlsx
+++ b/PROPUESTA_PRODUCCION_SUBLIMADO_ACTUALIZADA.xlsx
@@ -515,19 +515,19 @@
         <v>349</v>
       </c>
       <c r="C2" t="n">
-        <v>472</v>
+        <v>455</v>
       </c>
       <c r="D2" t="n">
-        <v>567</v>
+        <v>546</v>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F2" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>123</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3">
@@ -540,19 +540,19 @@
         <v>136</v>
       </c>
       <c r="C3" t="n">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="D3" t="n">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
         <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4">
@@ -565,19 +565,19 @@
         <v>485</v>
       </c>
       <c r="C4" t="n">
-        <v>777</v>
+        <v>750</v>
       </c>
       <c r="D4" t="n">
-        <v>933</v>
+        <v>900</v>
       </c>
       <c r="E4" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F4" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>292</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>32</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>34</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>61</v>
@@ -1256,25 +1256,25 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>20</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>21</v>
       </c>
       <c r="I12" s="6">
         <f>SUM(B12:H12)</f>
@@ -1454,10 +1454,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -1769,10 +1769,10 @@
         <v>20</v>
       </c>
       <c r="D17" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2356,10 +2356,10 @@
         <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -2377,10 +2377,10 @@
         <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2398,10 +2398,10 @@
         <v>16</v>
       </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -2419,10 +2419,10 @@
         <v>16</v>
       </c>
       <c r="D26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2440,10 +2440,10 @@
         <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -2461,10 +2461,10 @@
         <v>20</v>
       </c>
       <c r="D28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -2482,10 +2482,10 @@
         <v>20</v>
       </c>
       <c r="D29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/PROPUESTA_PRODUCCION_SUBLIMADO_ACTUALIZADA.xlsx
+++ b/PROPUESTA_PRODUCCION_SUBLIMADO_ACTUALIZADA.xlsx
@@ -540,19 +540,19 @@
         <v>136</v>
       </c>
       <c r="C3" t="n">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="D3" t="n">
-        <v>354</v>
+        <v>330</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>20.9</v>
       </c>
       <c r="G3" t="n">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4">
@@ -565,19 +565,19 @@
         <v>485</v>
       </c>
       <c r="C4" t="n">
-        <v>750</v>
+        <v>728</v>
       </c>
       <c r="D4" t="n">
-        <v>900</v>
+        <v>876</v>
       </c>
       <c r="E4" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="G4" t="n">
-        <v>265</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -1049,7 +1049,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>4</v>
@@ -1058,7 +1058,7 @@
         <v>5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>6</v>
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="G8" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="G8" s="5" t="n">
-        <v>21</v>
-      </c>
       <c r="H8" s="5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I8" s="6">
         <f>SUM(B8:H8)</f>
@@ -1256,25 +1256,25 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>21</v>
-      </c>
       <c r="G12" s="5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I12" s="6">
         <f>SUM(B12:H12)</f>
@@ -1957,10 +1957,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -2020,10 +2020,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -2062,10 +2062,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -2104,10 +2104,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -2146,10 +2146,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -2167,10 +2167,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -2188,10 +2188,10 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -2356,10 +2356,10 @@
         <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -2377,10 +2377,10 @@
         <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="25">
@@ -2398,10 +2398,10 @@
         <v>16</v>
       </c>
       <c r="D25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2419,10 +2419,10 @@
         <v>16</v>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27">
@@ -2440,10 +2440,10 @@
         <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2461,10 +2461,10 @@
         <v>20</v>
       </c>
       <c r="D28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2482,10 +2482,10 @@
         <v>20</v>
       </c>
       <c r="D29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
   </sheetData>

--- a/PROPUESTA_PRODUCCION_SUBLIMADO_ACTUALIZADA.xlsx
+++ b/PROPUESTA_PRODUCCION_SUBLIMADO_ACTUALIZADA.xlsx
@@ -540,19 +540,19 @@
         <v>136</v>
       </c>
       <c r="C3" t="n">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="D3" t="n">
-        <v>330</v>
+        <v>305</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
-        <v>137</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4">
@@ -565,19 +565,19 @@
         <v>485</v>
       </c>
       <c r="C4" t="n">
-        <v>728</v>
+        <v>707</v>
       </c>
       <c r="D4" t="n">
-        <v>876</v>
+        <v>851</v>
       </c>
       <c r="E4" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F4" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="G4" t="n">
-        <v>243</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>8</v>
@@ -1055,13 +1055,13 @@
         <v>4</v>
       </c>
       <c r="F6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="I6" s="6">
         <f>SUM(B6:H6)</f>
@@ -1120,19 +1120,19 @@
         <v>4</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>18</v>
       </c>
       <c r="I8" s="6">
         <f>SUM(B8:H8)</f>
@@ -1194,16 +1194,16 @@
         <v>4</v>
       </c>
       <c r="E10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="G10" s="5" t="n">
         <v>4</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I10" s="6">
         <f>SUM(B10:H10)</f>
@@ -1256,25 +1256,25 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>18</v>
       </c>
       <c r="I12" s="6">
         <f>SUM(B12:H12)</f>
@@ -1915,10 +1915,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1936,10 +1936,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1999,10 +1999,10 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="7">
@@ -2020,10 +2020,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -2041,10 +2041,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -2104,10 +2104,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -2146,10 +2146,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -2167,10 +2167,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -2188,10 +2188,10 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -2272,10 +2272,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -2293,10 +2293,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -2335,10 +2335,10 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2356,10 +2356,10 @@
         <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -2377,10 +2377,10 @@
         <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="25">
@@ -2398,10 +2398,10 @@
         <v>16</v>
       </c>
       <c r="D25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2419,10 +2419,10 @@
         <v>16</v>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E26" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="27">
@@ -2440,10 +2440,10 @@
         <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2461,10 +2461,10 @@
         <v>20</v>
       </c>
       <c r="D28" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2482,10 +2482,10 @@
         <v>20</v>
       </c>
       <c r="D29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E29" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
   </sheetData>

--- a/PROPUESTA_PRODUCCION_SUBLIMADO_ACTUALIZADA.xlsx
+++ b/PROPUESTA_PRODUCCION_SUBLIMADO_ACTUALIZADA.xlsx
@@ -515,19 +515,19 @@
         <v>349</v>
       </c>
       <c r="C2" t="n">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D2" t="n">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E2" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="G2" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3">
@@ -540,19 +540,19 @@
         <v>136</v>
       </c>
       <c r="C3" t="n">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="D3" t="n">
-        <v>305</v>
+        <v>271</v>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>20.4</v>
       </c>
       <c r="G3" t="n">
-        <v>116</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
@@ -565,19 +565,19 @@
         <v>485</v>
       </c>
       <c r="C4" t="n">
-        <v>707</v>
+        <v>679</v>
       </c>
       <c r="D4" t="n">
-        <v>851</v>
+        <v>815</v>
       </c>
       <c r="E4" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F4" t="n">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>222</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6" s="6">
         <f>SUM(B6:F6)</f>
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F8" s="5" t="n">
         <v>12</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>15</v>
       </c>
       <c r="G8" s="6">
         <f>SUM(B8:F8)</f>
@@ -778,19 +778,19 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G10" s="6">
         <f>SUM(B10:F10)</f>
@@ -835,16 +835,16 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>25</v>
@@ -1043,25 +1043,25 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>4</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I6" s="6">
         <f>SUM(B6:H6)</f>
@@ -1120,19 +1120,19 @@
         <v>4</v>
       </c>
       <c r="D8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>9</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="I8" s="6">
         <f>SUM(B8:H8)</f>
@@ -1194,13 +1194,13 @@
         <v>4</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>5</v>
@@ -1256,25 +1256,25 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>14</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I12" s="6">
         <f>SUM(B12:H12)</f>
@@ -1454,10 +1454,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -1475,10 +1475,10 @@
         <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1496,10 +1496,10 @@
         <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1517,10 +1517,10 @@
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -1538,10 +1538,10 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1580,10 +1580,10 @@
         <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -1601,10 +1601,10 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -1622,10 +1622,10 @@
         <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="11">
@@ -1643,10 +1643,10 @@
         <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="12">
@@ -1664,10 +1664,10 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1706,10 +1706,10 @@
         <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="15">
@@ -1727,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -1748,10 +1748,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -1769,10 +1769,10 @@
         <v>20</v>
       </c>
       <c r="D17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1790,10 +1790,10 @@
         <v>45</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -1811,10 +1811,10 @@
         <v>45</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -1832,10 +1832,10 @@
         <v>35</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E20" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1915,10 +1915,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1957,10 +1957,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -1999,10 +1999,10 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="7">
@@ -2020,10 +2020,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -2041,10 +2041,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -2104,10 +2104,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -2146,10 +2146,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -2167,10 +2167,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -2188,10 +2188,10 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -2272,10 +2272,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2314,10 +2314,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -2356,10 +2356,10 @@
         <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -2377,10 +2377,10 @@
         <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="25">
@@ -2398,10 +2398,10 @@
         <v>16</v>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="26">
@@ -2440,10 +2440,10 @@
         <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2461,10 +2461,10 @@
         <v>20</v>
       </c>
       <c r="D28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="29">
@@ -2482,10 +2482,10 @@
         <v>20</v>
       </c>
       <c r="D29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E29" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
